--- a/docs/reports/连通标注_2026-07-04_分表/6_宏观.xlsx
+++ b/docs/reports/连通标注_2026-07-04_分表/6_宏观.xlsx
@@ -1456,14 +1456,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K3" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K3" s="184" t="inlineStr">
+        <is>
+          <t>❌ 链接失效</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>无 BEA API provider 插件</t>
+          <t>验证:HTTP 404</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
       </c>
       <c r="K4" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1572,14 +1572,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K5" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K5" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>无 BLS API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;经API取数</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1632,7 @@
       </c>
       <c r="K6" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1688,14 +1688,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K7" s="183" t="inlineStr">
-        <is>
-          <t>🔑 需API密钥</t>
+      <c r="K7" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FRED API)</t>
+          <t xml:space="preserve">验证:ERR ConnectError: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in </t>
         </is>
       </c>
     </row>
@@ -1746,14 +1746,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K8" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K8" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>无 BLS API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;经API取数</t>
         </is>
       </c>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="K9" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -1862,14 +1862,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K10" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K10" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>无 US Census API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;经API取数</t>
         </is>
       </c>
     </row>
@@ -1920,14 +1920,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K11" s="183" t="inlineStr">
-        <is>
-          <t>🔑 需API密钥</t>
+      <c r="K11" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>配置 DATAHUB_*_API_KEY 后可用(FRED API)</t>
+          <t xml:space="preserve">验证:ERR ConnectError: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in </t>
         </is>
       </c>
     </row>
@@ -1978,14 +1978,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K12" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K12" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>无 USAspending API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2036,14 +2036,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K13" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K13" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>无 US Census API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;经API取数</t>
         </is>
       </c>
     </row>
@@ -2094,14 +2094,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K14" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K14" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>无 US Census API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;经API取数</t>
         </is>
       </c>
     </row>
@@ -2152,14 +2152,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K15" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K15" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>无 Eurostat API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2212,7 +2212,7 @@
       </c>
       <c r="K16" s="182" t="inlineStr">
         <is>
-          <t>✅ 联通可取数</t>
+          <t>✅ 联通·可取数</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2268,14 +2268,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K17" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K17" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>无 ECB Data API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2328,12 @@
       </c>
       <c r="K18" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -2386,12 +2386,12 @@
       </c>
       <c r="K19" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -2442,14 +2442,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K20" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K20" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>无 ONS API provider 插件</t>
+          <t xml:space="preserve">验证:ERR ConnectError: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in </t>
         </is>
       </c>
     </row>
@@ -2500,14 +2500,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K21" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K21" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>无 英国央行(BoE) API provider 插件</t>
+          <t xml:space="preserve">验证:ERR ConnectError: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in </t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="K22" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>HTTP 403,反爬/拒绝访问</t>
+          <t>HTTP 403,访问被拒</t>
         </is>
       </c>
     </row>
@@ -2616,14 +2616,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K23" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K23" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>无 e-Stat API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2674,14 +2674,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K24" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K24" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>无 日本央行(BOJ) API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2732,14 +2732,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K25" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K25" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2790,14 +2790,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K26" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K26" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2850,12 +2850,12 @@
       </c>
       <c r="K27" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -2906,14 +2906,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K28" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K28" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -2964,14 +2964,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K29" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K29" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>无 AKShare API (Python库) provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3024,12 +3024,12 @@
       </c>
       <c r="K30" s="183" t="inlineStr">
         <is>
-          <t>⚠️ 联通但为空</t>
+          <t>⚠️ 联通·暂无数据</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>请求成功但解析出 0 条(feed 为空或格式不符)</t>
+          <t>请求成功但当前无内容</t>
         </is>
       </c>
     </row>
@@ -3080,14 +3080,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K31" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K31" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3138,14 +3138,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K32" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K32" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:HTTP 412</t>
         </is>
       </c>
     </row>
@@ -3196,14 +3196,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K33" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K33" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>无 AKShare API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;经API取数</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3256,7 @@
       </c>
       <c r="K34" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3312,14 +3312,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K35" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K35" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>无 RBI DBIE API provider 插件</t>
+          <t xml:space="preserve">验证:ERR ConnectError: [SSL: CERTIFICATE_VERIFY_FAILED] certificate verify </t>
         </is>
       </c>
     </row>
@@ -3370,14 +3370,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K36" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K36" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>无 IBGE API provider 插件</t>
+          <t xml:space="preserve">验证:ERR ConnectError: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in </t>
         </is>
       </c>
     </row>
@@ -3428,14 +3428,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K37" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K37" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>无 巴西央行(BCB) API provider 插件</t>
+          <t xml:space="preserve">验证:ERR ConnectError: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in </t>
         </is>
       </c>
     </row>
@@ -3486,14 +3486,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K38" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K38" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>无 StatCan API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3544,14 +3544,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K39" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K39" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>无 BoC Valet API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3602,14 +3602,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K40" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K40" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>无 BoK ECOS API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3660,14 +3660,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K41" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K41" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>无 KOSIS API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3718,14 +3718,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K42" s="185" t="inlineStr">
-        <is>
-          <t>➖ 方式未支持</t>
+      <c r="K42" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>'RBA统计(CSV)' 无匹配 fetcher</t>
+          <t xml:space="preserve">验证:ERR ConnectError: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in </t>
         </is>
       </c>
     </row>
@@ -3776,14 +3776,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K43" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K43" s="184" t="inlineStr">
+        <is>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>无 ABS Data API provider 插件</t>
+          <t xml:space="preserve">验证:ERR ConnectError: [SSL: UNEXPECTED_EOF_WHILE_READING] EOF occurred in </t>
         </is>
       </c>
     </row>
@@ -3834,14 +3834,14 @@
           <t>P1</t>
         </is>
       </c>
-      <c r="K44" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K44" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>无 IMF API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;经API取数</t>
         </is>
       </c>
     </row>
@@ -3892,14 +3892,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K45" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K45" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>无 World Bank API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -3950,14 +3950,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K46" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K46" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>无 OECD API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 403),返回需鉴权;经API取数</t>
         </is>
       </c>
     </row>
@@ -4008,14 +4008,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K47" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K47" s="184" t="inlineStr">
+        <is>
+          <t>❌ 链接失效</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>无 BIS API (CSV) provider 插件</t>
+          <t>验证:HTTP 404</t>
         </is>
       </c>
     </row>
@@ -4066,14 +4066,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K48" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K48" s="184" t="inlineStr">
+        <is>
+          <t>❌ 链接失效</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>无 UN Comtrade API provider 插件</t>
+          <t>验证:HTTP 404</t>
         </is>
       </c>
     </row>
@@ -4126,7 +4126,7 @@
       </c>
       <c r="K49" s="184" t="inlineStr">
         <is>
-          <t>❌ 失败</t>
+          <t>❌ 不可联通</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4182,14 +4182,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K50" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K50" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>无 TradingEconomics API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费</t>
         </is>
       </c>
     </row>
@@ -4240,14 +4240,14 @@
           <t>P2</t>
         </is>
       </c>
-      <c r="K51" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K51" s="182" t="inlineStr">
+        <is>
+          <t>🟢 联通·免费</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>无 EIA API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);经API取数</t>
         </is>
       </c>
     </row>
@@ -4298,14 +4298,14 @@
           <t>P3</t>
         </is>
       </c>
-      <c r="K52" s="185" t="inlineStr">
-        <is>
-          <t>🔌 待开发插件</t>
+      <c r="K52" s="183" t="inlineStr">
+        <is>
+          <t>🟡 联通·需付费</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>无 CEIC API provider 插件</t>
+          <t>验证:接口/官网可达(HTTP 200);注册表:付费</t>
         </is>
       </c>
     </row>
